--- a/datoscrudos/datos-originales/deudapublica.xlsx
+++ b/datoscrudos/datos-originales/deudapublica.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estua\Desktop\CONFERENCIA\Conferencia-Econom-aA--Abril15-2026\datoscrudos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estua\Desktop\1ER SEMESTRE\DTT\DTT\CONFERENCIA CURSO\CONFERENCIA\Conferencia-Econom-aA--Abril15-2026\datoscrudos\datos-originales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB011177-01C6-41D9-93B9-4A00B35A3297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FA10DD-C997-49B0-A1D3-9AD9C8FEBB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{565C65A6-1476-462C-9C8F-BB4793634438}"/>
   </bookViews>
@@ -1569,14 +1569,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE0FCFE-7B32-42FD-AF1C-D27EF8E56A3E}">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>399</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>395</v>
       </c>
@@ -1603,8 +1603,12 @@
       <c r="D2" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" t="str">
+        <f>SUBSTITUTE(A2,"[+]","")</f>
+        <v xml:space="preserve">España </v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>392</v>
       </c>
@@ -1617,8 +1621,12 @@
       <c r="D3" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F66" si="0">SUBSTITUTE(A3,"[+]","")</f>
+        <v xml:space="preserve">Alemania </v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>389</v>
       </c>
@@ -1631,8 +1639,12 @@
       <c r="D4" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Reino Unido </v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>386</v>
       </c>
@@ -1645,8 +1657,12 @@
       <c r="D5" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Francia </v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>383</v>
       </c>
@@ -1659,8 +1675,12 @@
       <c r="D6" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Italia </v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>380</v>
       </c>
@@ -1673,8 +1693,12 @@
       <c r="D7" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Portugal </v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>378</v>
       </c>
@@ -1687,8 +1711,12 @@
       <c r="D8" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Estados Unidos </v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>375</v>
       </c>
@@ -1701,8 +1729,12 @@
       <c r="D9" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Japón </v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>372</v>
       </c>
@@ -1715,8 +1747,12 @@
       <c r="D10" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">China </v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>369</v>
       </c>
@@ -1729,8 +1765,12 @@
       <c r="D11" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Andorra </v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>367</v>
       </c>
@@ -1743,8 +1783,12 @@
       <c r="D12" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Emiratos Árabes Unidos </v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>365</v>
       </c>
@@ -1757,8 +1801,12 @@
       <c r="D13" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Afganistán </v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>363</v>
       </c>
@@ -1771,8 +1819,12 @@
       <c r="D14" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Antigua y Barbuda </v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>361</v>
       </c>
@@ -1785,8 +1837,12 @@
       <c r="D15" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Albania </v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>359</v>
       </c>
@@ -1799,8 +1855,12 @@
       <c r="D16" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Armenia </v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>357</v>
       </c>
@@ -1813,8 +1873,12 @@
       <c r="D17" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Angola </v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>355</v>
       </c>
@@ -1827,8 +1891,12 @@
       <c r="D18" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Argentina </v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>353</v>
       </c>
@@ -1841,8 +1909,12 @@
       <c r="D19" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Austria </v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>351</v>
       </c>
@@ -1855,8 +1927,12 @@
       <c r="D20" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Australia </v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>349</v>
       </c>
@@ -1869,8 +1945,12 @@
       <c r="D21" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Azerbaiyán </v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>347</v>
       </c>
@@ -1883,8 +1963,12 @@
       <c r="D22" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bosnia y Herzegovina </v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>345</v>
       </c>
@@ -1897,8 +1981,12 @@
       <c r="D23" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Barbados </v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>343</v>
       </c>
@@ -1911,8 +1999,12 @@
       <c r="D24" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bangladés </v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>341</v>
       </c>
@@ -1925,8 +2017,12 @@
       <c r="D25" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bélgica </v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>339</v>
       </c>
@@ -1939,8 +2035,12 @@
       <c r="D26" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Burkina Faso </v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>337</v>
       </c>
@@ -1953,8 +2053,12 @@
       <c r="D27" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bulgaria </v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>335</v>
       </c>
@@ -1967,8 +2071,12 @@
       <c r="D28" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Baréin </v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>333</v>
       </c>
@@ -1981,8 +2089,12 @@
       <c r="D29" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Burundi </v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>331</v>
       </c>
@@ -1995,8 +2107,12 @@
       <c r="D30" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Benin </v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>329</v>
       </c>
@@ -2009,8 +2125,12 @@
       <c r="D31" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Brunéi </v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>327</v>
       </c>
@@ -2023,8 +2143,12 @@
       <c r="D32" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bolivia </v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>325</v>
       </c>
@@ -2037,8 +2161,12 @@
       <c r="D33" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Brasil </v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>322</v>
       </c>
@@ -2051,8 +2179,12 @@
       <c r="D34" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bahamas </v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>320</v>
       </c>
@@ -2065,8 +2197,12 @@
       <c r="D35" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bután </v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>318</v>
       </c>
@@ -2079,8 +2215,12 @@
       <c r="D36" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Botsuana </v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>316</v>
       </c>
@@ -2093,8 +2233,12 @@
       <c r="D37" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Bielorrusia </v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>314</v>
       </c>
@@ -2107,8 +2251,12 @@
       <c r="D38" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Belice </v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>312</v>
       </c>
@@ -2121,8 +2269,12 @@
       <c r="D39" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Canadá </v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>309</v>
       </c>
@@ -2135,8 +2287,12 @@
       <c r="D40" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">República Democrática del Congo </v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>307</v>
       </c>
@@ -2149,8 +2305,12 @@
       <c r="D41" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">República Centroafricana </v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>305</v>
       </c>
@@ -2163,8 +2323,12 @@
       <c r="D42" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">República del Congo </v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>303</v>
       </c>
@@ -2177,8 +2341,12 @@
       <c r="D43" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Suiza </v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>301</v>
       </c>
@@ -2191,8 +2359,12 @@
       <c r="D44" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Costa de Marfil </v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>299</v>
       </c>
@@ -2205,8 +2377,12 @@
       <c r="D45" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Chile </v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>297</v>
       </c>
@@ -2219,8 +2395,12 @@
       <c r="D46" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Camerún </v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>295</v>
       </c>
@@ -2233,8 +2413,12 @@
       <c r="D47" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Colombia </v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>293</v>
       </c>
@@ -2247,8 +2431,12 @@
       <c r="D48" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Costa Rica </v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>291</v>
       </c>
@@ -2261,8 +2449,12 @@
       <c r="D49" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Cabo Verde </v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>289</v>
       </c>
@@ -2275,8 +2467,12 @@
       <c r="D50" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F50" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Chipre </v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>287</v>
       </c>
@@ -2289,8 +2485,12 @@
       <c r="D51" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F51" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Chequia </v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>285</v>
       </c>
@@ -2303,8 +2503,12 @@
       <c r="D52" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F52" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Yibuti </v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>283</v>
       </c>
@@ -2317,8 +2521,12 @@
       <c r="D53" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F53" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Dinamarca </v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>281</v>
       </c>
@@ -2331,8 +2539,12 @@
       <c r="D54" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F54" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Dominica </v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>279</v>
       </c>
@@ -2345,8 +2557,12 @@
       <c r="D55" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F55" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">República Dominicana </v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>277</v>
       </c>
@@ -2359,8 +2575,12 @@
       <c r="D56" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F56" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Argelia </v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>275</v>
       </c>
@@ -2373,8 +2593,12 @@
       <c r="D57" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F57" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Ecuador </v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>273</v>
       </c>
@@ -2387,8 +2611,12 @@
       <c r="D58" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F58" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Estonia </v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>271</v>
       </c>
@@ -2401,8 +2629,12 @@
       <c r="D59" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F59" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Egipto </v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>269</v>
       </c>
@@ -2415,8 +2647,12 @@
       <c r="D60" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F60" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Eritrea </v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>267</v>
       </c>
@@ -2429,8 +2665,12 @@
       <c r="D61" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F61" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Etiopía </v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>265</v>
       </c>
@@ -2443,8 +2683,12 @@
       <c r="D62" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F62" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Finlandia </v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>263</v>
       </c>
@@ -2457,8 +2701,12 @@
       <c r="D63" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F63" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Fiyi </v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>261</v>
       </c>
@@ -2471,8 +2719,12 @@
       <c r="D64" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F64" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Estados Federados de Micronesia </v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>259</v>
       </c>
@@ -2485,8 +2737,12 @@
       <c r="D65" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F65" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Gabón </v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>257</v>
       </c>
@@ -2499,8 +2755,12 @@
       <c r="D66" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F66" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Granada </v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>255</v>
       </c>
@@ -2513,8 +2773,12 @@
       <c r="D67" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F67" t="str">
+        <f t="shared" ref="F67:F130" si="1">SUBSTITUTE(A67,"[+]","")</f>
+        <v xml:space="preserve">Georgia </v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>253</v>
       </c>
@@ -2527,8 +2791,12 @@
       <c r="D68" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F68" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Ghana </v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>251</v>
       </c>
@@ -2541,8 +2809,12 @@
       <c r="D69" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F69" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Gambia </v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>249</v>
       </c>
@@ -2555,8 +2827,12 @@
       <c r="D70" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F70" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Guinea </v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>247</v>
       </c>
@@ -2569,8 +2845,12 @@
       <c r="D71" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F71" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Guinea Ecuatorial </v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>245</v>
       </c>
@@ -2583,8 +2863,12 @@
       <c r="D72" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F72" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Grecia </v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>243</v>
       </c>
@@ -2597,8 +2881,12 @@
       <c r="D73" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F73" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Guatemala </v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>241</v>
       </c>
@@ -2611,8 +2899,12 @@
       <c r="D74" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F74" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Guinea-Bisáu </v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>239</v>
       </c>
@@ -2625,8 +2917,12 @@
       <c r="D75" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F75" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Guyana </v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>237</v>
       </c>
@@ -2639,8 +2935,12 @@
       <c r="D76" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F76" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Hong Kong </v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>235</v>
       </c>
@@ -2653,8 +2953,12 @@
       <c r="D77" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F77" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Honduras </v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>233</v>
       </c>
@@ -2667,8 +2971,12 @@
       <c r="D78" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F78" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Croacia </v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>231</v>
       </c>
@@ -2681,8 +2989,12 @@
       <c r="D79" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F79" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Haití </v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>229</v>
       </c>
@@ -2695,8 +3007,12 @@
       <c r="D80" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F80" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Hungría </v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>227</v>
       </c>
@@ -2709,8 +3025,12 @@
       <c r="D81" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F81" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Indonesia </v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>225</v>
       </c>
@@ -2723,8 +3043,12 @@
       <c r="D82" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F82" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Irlanda </v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>223</v>
       </c>
@@ -2737,8 +3061,12 @@
       <c r="D83" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F83" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Israel </v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>221</v>
       </c>
@@ -2751,8 +3079,12 @@
       <c r="D84" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F84" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">India </v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>218</v>
       </c>
@@ -2765,8 +3097,12 @@
       <c r="D85" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F85" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Irak </v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>216</v>
       </c>
@@ -2779,8 +3115,12 @@
       <c r="D86" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F86" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Irán </v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>214</v>
       </c>
@@ -2793,8 +3133,12 @@
       <c r="D87" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F87" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Islandia </v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>212</v>
       </c>
@@ -2807,8 +3151,12 @@
       <c r="D88" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F88" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Jamaica </v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>210</v>
       </c>
@@ -2821,8 +3169,12 @@
       <c r="D89" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F89" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Jordania </v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>208</v>
       </c>
@@ -2835,8 +3187,12 @@
       <c r="D90" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F90" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Kenia </v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>206</v>
       </c>
@@ -2849,8 +3205,12 @@
       <c r="D91" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F91" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Kirguistán </v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>204</v>
       </c>
@@ -2863,8 +3223,12 @@
       <c r="D92" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F92" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Camboya </v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>202</v>
       </c>
@@ -2877,8 +3241,12 @@
       <c r="D93" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F93" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Kiribati </v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>200</v>
       </c>
@@ -2891,8 +3259,12 @@
       <c r="D94" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F94" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Comoras </v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>198</v>
       </c>
@@ -2905,8 +3277,12 @@
       <c r="D95" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F95" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">San Cristóbal y Nieves </v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>196</v>
       </c>
@@ -2919,8 +3295,12 @@
       <c r="D96" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F96" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Corea del Sur </v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>194</v>
       </c>
@@ -2933,8 +3313,12 @@
       <c r="D97" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F97" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Kuwait </v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -2947,8 +3331,12 @@
       <c r="D98" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F98" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Kazajistán </v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>190</v>
       </c>
@@ -2961,8 +3349,12 @@
       <c r="D99" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F99" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Laos </v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>188</v>
       </c>
@@ -2975,8 +3367,12 @@
       <c r="D100" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F100" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Líbano </v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>186</v>
       </c>
@@ -2989,8 +3385,12 @@
       <c r="D101" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F101" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Santa Lucía </v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>184</v>
       </c>
@@ -3003,8 +3403,12 @@
       <c r="D102" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F102" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Liechtenstein </v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>182</v>
       </c>
@@ -3017,8 +3421,12 @@
       <c r="D103" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F103" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Sri Lanka </v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>180</v>
       </c>
@@ -3031,8 +3439,12 @@
       <c r="D104" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F104" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Liberia </v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>178</v>
       </c>
@@ -3045,8 +3457,12 @@
       <c r="D105" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F105" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Lesoto </v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>176</v>
       </c>
@@ -3059,8 +3475,12 @@
       <c r="D106" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F106" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Lituania </v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>174</v>
       </c>
@@ -3073,8 +3493,12 @@
       <c r="D107" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F107" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Luxemburgo </v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>172</v>
       </c>
@@ -3087,8 +3511,12 @@
       <c r="D108" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F108" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Letonia </v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>170</v>
       </c>
@@ -3101,8 +3529,12 @@
       <c r="D109" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F109" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Libia </v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>168</v>
       </c>
@@ -3115,8 +3547,12 @@
       <c r="D110" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F110" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Marruecos </v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>166</v>
       </c>
@@ -3129,8 +3565,12 @@
       <c r="D111" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F111" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Moldavia </v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>164</v>
       </c>
@@ -3143,8 +3583,12 @@
       <c r="D112" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F112" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Montenegro </v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>162</v>
       </c>
@@ -3157,8 +3601,12 @@
       <c r="D113" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F113" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Madagascar </v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>160</v>
       </c>
@@ -3171,8 +3619,12 @@
       <c r="D114" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F114" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Islas Marshall </v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>158</v>
       </c>
@@ -3185,8 +3637,12 @@
       <c r="D115" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F115" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Macedonia del Norte </v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>156</v>
       </c>
@@ -3199,8 +3655,12 @@
       <c r="D116" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F116" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Malí </v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>154</v>
       </c>
@@ -3213,8 +3673,12 @@
       <c r="D117" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F117" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Myanmar </v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>152</v>
       </c>
@@ -3227,8 +3691,12 @@
       <c r="D118" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F118" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Mongolia </v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>150</v>
       </c>
@@ -3241,8 +3709,12 @@
       <c r="D119" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F119" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Mauritania </v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3255,8 +3727,12 @@
       <c r="D120" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F120" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Malta </v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>146</v>
       </c>
@@ -3269,8 +3745,12 @@
       <c r="D121" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F121" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Mauricio </v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>144</v>
       </c>
@@ -3283,8 +3763,12 @@
       <c r="D122" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F122" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Maldivas </v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>142</v>
       </c>
@@ -3297,8 +3781,12 @@
       <c r="D123" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F123" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Malaui </v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>140</v>
       </c>
@@ -3311,8 +3799,12 @@
       <c r="D124" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F124" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">México </v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>137</v>
       </c>
@@ -3325,8 +3817,12 @@
       <c r="D125" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F125" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Malasia </v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>135</v>
       </c>
@@ -3339,8 +3835,12 @@
       <c r="D126" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F126" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Mozambique </v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>133</v>
       </c>
@@ -3353,8 +3853,12 @@
       <c r="D127" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F127" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Namibia </v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>131</v>
       </c>
@@ -3367,8 +3871,12 @@
       <c r="D128" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F128" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Níger </v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>129</v>
       </c>
@@ -3381,8 +3889,12 @@
       <c r="D129" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F129" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Nigeria </v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -3395,8 +3907,12 @@
       <c r="D130" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F130" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Nicaragua </v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>125</v>
       </c>
@@ -3409,8 +3925,12 @@
       <c r="D131" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F131" t="str">
+        <f t="shared" ref="F131:F193" si="2">SUBSTITUTE(A131,"[+]","")</f>
+        <v xml:space="preserve">Países Bajos </v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>123</v>
       </c>
@@ -3423,8 +3943,12 @@
       <c r="D132" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F132" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Noruega </v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>121</v>
       </c>
@@ -3437,8 +3961,12 @@
       <c r="D133" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F133" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Nepal </v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>119</v>
       </c>
@@ -3451,8 +3979,12 @@
       <c r="D134" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F134" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Nauru </v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>117</v>
       </c>
@@ -3465,8 +3997,12 @@
       <c r="D135" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F135" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Nueva Zelanda </v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>115</v>
       </c>
@@ -3479,8 +4015,12 @@
       <c r="D136" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F136" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Omán </v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>113</v>
       </c>
@@ -3493,8 +4033,12 @@
       <c r="D137" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F137" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Panamá </v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>111</v>
       </c>
@@ -3507,8 +4051,12 @@
       <c r="D138" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F138" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Perú </v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -3521,8 +4069,12 @@
       <c r="D139" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F139" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Papúa Nueva Guinea </v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>107</v>
       </c>
@@ -3535,8 +4087,12 @@
       <c r="D140" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F140" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Filipinas </v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>105</v>
       </c>
@@ -3549,8 +4105,12 @@
       <c r="D141" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F141" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Pakistán </v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>103</v>
       </c>
@@ -3563,8 +4123,12 @@
       <c r="D142" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F142" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Polonia </v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>101</v>
       </c>
@@ -3577,8 +4141,12 @@
       <c r="D143" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F143" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Estado de Palestina </v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>99</v>
       </c>
@@ -3591,8 +4159,12 @@
       <c r="D144" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F144" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Palaos </v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>97</v>
       </c>
@@ -3605,8 +4177,12 @@
       <c r="D145" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F145" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Paraguay </v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>95</v>
       </c>
@@ -3619,8 +4195,12 @@
       <c r="D146" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F146" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Catar </v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>93</v>
       </c>
@@ -3633,8 +4213,12 @@
       <c r="D147" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F147" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Rumanía </v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>91</v>
       </c>
@@ -3647,8 +4231,12 @@
       <c r="D148" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F148" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Serbia </v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>89</v>
       </c>
@@ -3661,8 +4249,12 @@
       <c r="D149" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F149" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Rusia </v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>87</v>
       </c>
@@ -3675,8 +4267,12 @@
       <c r="D150" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F150" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Ruanda </v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>85</v>
       </c>
@@ -3689,8 +4285,12 @@
       <c r="D151" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F151" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Arabia Saudita </v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>83</v>
       </c>
@@ -3703,8 +4303,12 @@
       <c r="D152" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F152" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Islas Salomón </v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>81</v>
       </c>
@@ -3717,8 +4321,12 @@
       <c r="D153" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F153" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Seychelles </v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +4339,12 @@
       <c r="D154" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F154" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Sudán </v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>77</v>
       </c>
@@ -3745,8 +4357,12 @@
       <c r="D155" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F155" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Suecia </v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>75</v>
       </c>
@@ -3759,8 +4375,12 @@
       <c r="D156" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F156" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Singapur </v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>73</v>
       </c>
@@ -3773,8 +4393,12 @@
       <c r="D157" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F157" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Eslovenia </v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>71</v>
       </c>
@@ -3787,8 +4411,12 @@
       <c r="D158" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F158" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Eslovaquia </v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>69</v>
       </c>
@@ -3801,8 +4429,12 @@
       <c r="D159" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F159" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Sierra Leona </v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>67</v>
       </c>
@@ -3815,8 +4447,12 @@
       <c r="D160" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F160" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">San Marino </v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>65</v>
       </c>
@@ -3829,8 +4465,12 @@
       <c r="D161" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F161" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Senegal </v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>63</v>
       </c>
@@ -3843,8 +4483,12 @@
       <c r="D162" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F162" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Surinam </v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>61</v>
       </c>
@@ -3857,8 +4501,12 @@
       <c r="D163" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F163" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Sudán del Sur </v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>59</v>
       </c>
@@ -3871,8 +4519,12 @@
       <c r="D164" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F164" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Santo Tomé y Príncipe </v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>57</v>
       </c>
@@ -3885,8 +4537,12 @@
       <c r="D165" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F165" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">El Salvador </v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>55</v>
       </c>
@@ -3899,8 +4555,12 @@
       <c r="D166" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F166" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Siria </v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>53</v>
       </c>
@@ -3913,8 +4573,12 @@
       <c r="D167" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F167" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Eswatini </v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>51</v>
       </c>
@@ -3927,8 +4591,12 @@
       <c r="D168" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F168" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Chad </v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>49</v>
       </c>
@@ -3941,8 +4609,12 @@
       <c r="D169" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F169" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Togo </v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>47</v>
       </c>
@@ -3955,8 +4627,12 @@
       <c r="D170" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F170" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Tailandia </v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>45</v>
       </c>
@@ -3969,8 +4645,12 @@
       <c r="D171" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F171" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Tayikistán </v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>43</v>
       </c>
@@ -3983,8 +4663,12 @@
       <c r="D172" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F172" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Timor Oriental </v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>41</v>
       </c>
@@ -3997,8 +4681,12 @@
       <c r="D173" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F173" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Turkmenistán </v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -4011,8 +4699,12 @@
       <c r="D174" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F174" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Túnez </v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>37</v>
       </c>
@@ -4025,8 +4717,12 @@
       <c r="D175" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F175" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Tonga </v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -4039,8 +4735,12 @@
       <c r="D176" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F176" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Türkiye </v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>33</v>
       </c>
@@ -4053,8 +4753,12 @@
       <c r="D177" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F177" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Trinidad y Tobago </v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>31</v>
       </c>
@@ -4067,8 +4771,12 @@
       <c r="D178" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F178" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Tuvalu </v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>29</v>
       </c>
@@ -4081,8 +4789,12 @@
       <c r="D179" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F179" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Taiwan </v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>27</v>
       </c>
@@ -4095,8 +4807,12 @@
       <c r="D180" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F180" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Tanzania </v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>25</v>
       </c>
@@ -4109,8 +4825,12 @@
       <c r="D181" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F181" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Ucrania </v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>23</v>
       </c>
@@ -4123,8 +4843,12 @@
       <c r="D182" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F182" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Uganda </v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>21</v>
       </c>
@@ -4137,8 +4861,12 @@
       <c r="D183" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F183" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Uruguay </v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>19</v>
       </c>
@@ -4151,8 +4879,12 @@
       <c r="D184" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F184" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Uzbekistán </v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -4165,8 +4897,12 @@
       <c r="D185" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F185" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">San Vicente y las Granadinas </v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -4179,8 +4915,12 @@
       <c r="D186" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F186" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Venezuela </v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -4193,8 +4933,12 @@
       <c r="D187" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F187" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Viet Nam </v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>11</v>
       </c>
@@ -4207,8 +4951,12 @@
       <c r="D188" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F188" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Vanuatu </v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -4221,8 +4969,12 @@
       <c r="D189" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F189" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Samoa </v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>7</v>
       </c>
@@ -4235,8 +4987,12 @@
       <c r="D190" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F190" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Yemen </v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -4249,8 +5005,12 @@
       <c r="D191" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F191" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Sudáfrica </v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>3</v>
       </c>
@@ -4263,8 +5023,12 @@
       <c r="D192" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F192" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Zambia </v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1</v>
       </c>
@@ -4276,6 +5040,10 @@
       </c>
       <c r="D193" t="s">
         <v>0</v>
+      </c>
+      <c r="F193" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Zimbabue </v>
       </c>
     </row>
   </sheetData>
